--- a/data/08_transactions.xlsx
+++ b/data/08_transactions.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R69d582fe8b83441b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Deals" sheetId="2" r:id="R1ce4a9af1799422b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions V125" sheetId="3" r:id="R399ada3dfe644645"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transaction Approvals" sheetId="4" r:id="R854e12c1ba7f49e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transaction Status History" sheetId="5" r:id="R00097b1c7eda4334"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transaction Asset Links" sheetId="6" r:id="R20eadb3101e348c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vessel Transactions" sheetId="7" r:id="R899444246d634b0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Control History" sheetId="8" r:id="Ra8e130ddacdb4133"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rb923a94c29874aa2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Deals" sheetId="2" r:id="Rede6528bafd54b87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions V125" sheetId="3" r:id="Rf3660c77968b4c73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transaction Approvals" sheetId="4" r:id="Rd4e5b14479404906"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transaction Status History" sheetId="5" r:id="Rfd019edbcbe24b72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transaction Asset Links" sheetId="6" r:id="Racc5572bf58f4005"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vessel Transactions" sheetId="7" r:id="Re64ef46f7ada463f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Control History" sheetId="8" r:id="R8ba48a13be504d47"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1310,7 +1310,7 @@
         <x:v>IDEAL_0015</x:v>
       </x:c>
       <x:c r="B16" s="14" t="str">
-        <x:v>2026-09-07</x:v>
+        <x:v>2026-09-09</x:v>
       </x:c>
       <x:c r="C16" s="14"/>
       <x:c r="D16" s="14" t="str">
@@ -1333,26 +1333,32 @@
         <x:v>United States</x:v>
       </x:c>
       <x:c r="K16" s="14" t="str">
-        <x:v>Potential competing bid</x:v>
+        <x:v>Non-binding indication of interest</x:v>
       </x:c>
       <x:c r="L16" s="14"/>
-      <x:c r="M16" s="14"/>
-      <x:c r="N16" s="14"/>
-      <x:c r="O16" s="14"/>
+      <x:c r="M16" s="14" t="str">
+        <x:v>1250000000</x:v>
+      </x:c>
+      <x:c r="N16" s="14" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="O16" s="14" t="str">
+        <x:v>Standalone platform proposed</x:v>
+      </x:c>
       <x:c r="P16" s="14" t="str">
-        <x:v>Preliminary discussions / no proposal</x:v>
+        <x:v>Under review / due diligence</x:v>
       </x:c>
       <x:c r="Q16" s="14" t="str">
-        <x:v>National-security / regulatory sensitivity</x:v>
+        <x:v>U.S. government approval required for any control change</x:v>
       </x:c>
       <x:c r="R16" s="14" t="str">
-        <x:v>SRC_0348</x:v>
+        <x:v>SRC260910_007</x:v>
       </x:c>
       <x:c r="S16" s="14" t="str">
-        <x:v>https://maritime-executive.com/article/potential-u-s-bidder-emerges-to-challenge-hanwha-for-austal-usa</x:v>
+        <x:v>https://maritime-executive.com/article/us-investors-top-hanwha-s-bid-for-austal-usa</x:v>
       </x:c>
       <x:c r="T16" s="14" t="str">
-        <x:v>Austal confirmed preliminary discussions; no formal proposal at cited date.</x:v>
+        <x:v>Wildcat indicated $1.25bn-$1.35bn EV; stored low end in value field. Hanwha range reported at $1.05bn-$1.20bn.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1405,6 +1411,438 @@
       </x:c>
       <x:c r="T17" s="14" t="str">
         <x:v>30-day extension reported; revised proposal expected by end-Sep 2026.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>IDEAL_0017</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C18"/>
+      <x:c r="D18" t="str">
+        <x:v>COMP_COCHIN_SHIPYARD</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>COMP_DRYDOCKS_WORLD</x:v>
+      </x:c>
+      <x:c r="F18"/>
+      <x:c r="G18" t="str">
+        <x:v>ASSET_KOCHI_ISRF</x:v>
+      </x:c>
+      <x:c r="H18" t="str">
+        <x:v>International Ship Repair Facility (ISRF), Kochi</x:v>
+      </x:c>
+      <x:c r="I18" t="str">
+        <x:v>Ship repair / shipyard</x:v>
+      </x:c>
+      <x:c r="J18" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="K18" t="str">
+        <x:v>50:50 joint venture / asset transfer</x:v>
+      </x:c>
+      <x:c r="L18" t="str">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="M18" t="str">
+        <x:v>189000000</x:v>
+      </x:c>
+      <x:c r="N18" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="O18" t="str">
+        <x:v>Drydocks World management lead</x:v>
+      </x:c>
+      <x:c r="P18" t="str">
+        <x:v>Announced / approvals pending</x:v>
+      </x:c>
+      <x:c r="Q18" t="str">
+        <x:v>Multiple Indian approvals and shareholder approval required</x:v>
+      </x:c>
+      <x:c r="R18" t="str">
+        <x:v>SRC260910_003</x:v>
+      </x:c>
+      <x:c r="S18" t="str">
+        <x:v>https://splash247.com/cochin-and-drydocks-world-seal-kochi-repair-venture/</x:v>
+      </x:c>
+      <x:c r="T18" t="str">
+        <x:v>Cochin to transfer facility to JV at not less than $189m; Drydocks World to nominate 3 of 5 directors.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>IDEAL_0018</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19" t="str">
+        <x:v>PORTG0358</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>Xiangshan Port offshore-wind base</x:v>
+      </x:c>
+      <x:c r="I19" t="str">
+        <x:v>Port infrastructure</x:v>
+      </x:c>
+      <x:c r="J19" t="str">
+        <x:v>China</x:v>
+      </x:c>
+      <x:c r="K19" t="str">
+        <x:v>Greenfield specialist port development</x:v>
+      </x:c>
+      <x:c r="L19"/>
+      <x:c r="M19" t="str">
+        <x:v>223000000</x:v>
+      </x:c>
+      <x:c r="N19" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="O19"/>
+      <x:c r="P19" t="str">
+        <x:v>Approved / pre-construction</x:v>
+      </x:c>
+      <x:c r="Q19" t="str">
+        <x:v>Design and construction approvals progressing</x:v>
+      </x:c>
+      <x:c r="R19" t="str">
+        <x:v>SRC260910_010</x:v>
+      </x:c>
+      <x:c r="S19" t="str">
+        <x:v>https://splash247.com/ningbo-clears-223m-offshore-wind-port-development/</x:v>
+      </x:c>
+      <x:c r="T19" t="str">
+        <x:v>First phase includes 50,000-tonne ro-ro and multipurpose berths.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>IDEAL_0019</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20" t="str">
+        <x:v>PORTG0170</x:v>
+      </x:c>
+      <x:c r="H20" t="str">
+        <x:v>Port of Colombo digital infrastructure</x:v>
+      </x:c>
+      <x:c r="I20" t="str">
+        <x:v>Port digital infrastructure</x:v>
+      </x:c>
+      <x:c r="J20" t="str">
+        <x:v>Sri Lanka</x:v>
+      </x:c>
+      <x:c r="K20" t="str">
+        <x:v>Government assistance / digital upgrade</x:v>
+      </x:c>
+      <x:c r="L20"/>
+      <x:c r="M20" t="str">
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="N20" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="O20"/>
+      <x:c r="P20" t="str">
+        <x:v>Proposed</x:v>
+      </x:c>
+      <x:c r="Q20" t="str">
+        <x:v>U.S. congressional approval still required</x:v>
+      </x:c>
+      <x:c r="R20" t="str">
+        <x:v>SRC260910_011</x:v>
+      </x:c>
+      <x:c r="S20" t="str">
+        <x:v>https://splash247.com/us-lines-up-15m-for-colombo-port-digital-upgrade/</x:v>
+      </x:c>
+      <x:c r="T20" t="str">
+        <x:v>State Department approval reported; aimed at turnaround and waiting-time improvement.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>IDEAL_0020</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="D21"/>
+      <x:c r="E21"/>
+      <x:c r="F21" t="str">
+        <x:v>Australian federal and New South Wales governments</x:v>
+      </x:c>
+      <x:c r="G21" t="str">
+        <x:v>PORTG0356</x:v>
+      </x:c>
+      <x:c r="H21" t="str">
+        <x:v>Port of Newcastle freight access / M1 extension</x:v>
+      </x:c>
+      <x:c r="I21" t="str">
+        <x:v>Road / port-hinterland infrastructure</x:v>
+      </x:c>
+      <x:c r="J21" t="str">
+        <x:v>Australia</x:v>
+      </x:c>
+      <x:c r="K21" t="str">
+        <x:v>Public infrastructure upgrade</x:v>
+      </x:c>
+      <x:c r="L21"/>
+      <x:c r="M21" t="str">
+        <x:v>1620000000</x:v>
+      </x:c>
+      <x:c r="N21" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="O21"/>
+      <x:c r="P21" t="str">
+        <x:v>Entering service</x:v>
+      </x:c>
+      <x:c r="Q21" t="str">
+        <x:v>Completed public works</x:v>
+      </x:c>
+      <x:c r="R21" t="str">
+        <x:v>SRC260910_012</x:v>
+      </x:c>
+      <x:c r="S21" t="str">
+        <x:v>https://splash247.com/newcastle-gets-1-62bn-freight-access-upgrade/</x:v>
+      </x:c>
+      <x:c r="T21" t="str">
+        <x:v>A$2.24bn programme; strengthens Sydney-Brisbane freight corridor access.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>IDEAL_0021</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C22"/>
+      <x:c r="D22" t="str">
+        <x:v>COMP_GUOYOU_RESOURCES</x:v>
+      </x:c>
+      <x:c r="E22"/>
+      <x:c r="F22" t="str">
+        <x:v>Mangystau regional authorities</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>PORTG0141</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
+        <x:v>Caspian port and logistics hub / Kuryk area</x:v>
+      </x:c>
+      <x:c r="I22" t="str">
+        <x:v>Port / logistics hub</x:v>
+      </x:c>
+      <x:c r="J22" t="str">
+        <x:v>Kazakhstan</x:v>
+      </x:c>
+      <x:c r="K22" t="str">
+        <x:v>Greenfield multimodal hub</x:v>
+      </x:c>
+      <x:c r="L22"/>
+      <x:c r="M22" t="str">
+        <x:v>1000000000</x:v>
+      </x:c>
+      <x:c r="N22" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="O22" t="str">
+        <x:v>Developer-led project</x:v>
+      </x:c>
+      <x:c r="P22" t="str">
+        <x:v>Design / survey</x:v>
+      </x:c>
+      <x:c r="Q22" t="str">
+        <x:v>Regional approvals / project development</x:v>
+      </x:c>
+      <x:c r="R22" t="str">
+        <x:v>SRC260910_014</x:v>
+      </x:c>
+      <x:c r="S22" t="str">
+        <x:v>https://splash247.com/kazakhstan-advances-1bn-caspian-port-hub/</x:v>
+      </x:c>
+      <x:c r="T22" t="str">
+        <x:v>Seven berths, rail/road, ferry and shipbuilding-repair infrastructure; first phase about $300m.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>IDEAL_0022</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C23"/>
+      <x:c r="D23" t="str">
+        <x:v>COMP_TIL</x:v>
+      </x:c>
+      <x:c r="E23"/>
+      <x:c r="F23" t="str">
+        <x:v>Valencia Port Authority</x:v>
+      </x:c>
+      <x:c r="G23" t="str">
+        <x:v>PORTG0159</x:v>
+      </x:c>
+      <x:c r="H23" t="str">
+        <x:v>Valencia North Container Terminal</x:v>
+      </x:c>
+      <x:c r="I23" t="str">
+        <x:v>Container terminal</x:v>
+      </x:c>
+      <x:c r="J23" t="str">
+        <x:v>Spain</x:v>
+      </x:c>
+      <x:c r="K23" t="str">
+        <x:v>50-year concession / terminal development</x:v>
+      </x:c>
+      <x:c r="L23"/>
+      <x:c r="M23" t="str">
+        <x:v>767000000</x:v>
+      </x:c>
+      <x:c r="N23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="O23" t="str">
+        <x:v>Terminal Investment Limited concessionaire</x:v>
+      </x:c>
+      <x:c r="P23" t="str">
+        <x:v>Court challenge rejected / project progressing</x:v>
+      </x:c>
+      <x:c r="Q23" t="str">
+        <x:v>Environmental challenge dismissed</x:v>
+      </x:c>
+      <x:c r="R23" t="str">
+        <x:v>SRC260910_015</x:v>
+      </x:c>
+      <x:c r="S23" t="str">
+        <x:v>https://splash247.com/valencia-north-terminal-survives-environmental-court-challenge/</x:v>
+      </x:c>
+      <x:c r="T23" t="str">
+        <x:v>Tender budget exceeds €660m; designed capacity approaches 4.8m TEU/year.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>IDEAL_0023</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C24"/>
+      <x:c r="D24" t="str">
+        <x:v>COMP_DPW</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>COMP_GULFCAP_AFRICA</x:v>
+      </x:c>
+      <x:c r="F24"/>
+      <x:c r="G24" t="str">
+        <x:v>ASSET_MOMBASA_IP</x:v>
+      </x:c>
+      <x:c r="H24" t="str">
+        <x:v>Mombasa Industrial Park</x:v>
+      </x:c>
+      <x:c r="I24" t="str">
+        <x:v>Industrial park / logistics real estate</x:v>
+      </x:c>
+      <x:c r="J24" t="str">
+        <x:v>Kenya</x:v>
+      </x:c>
+      <x:c r="K24" t="str">
+        <x:v>Joint venture / SEZ development</x:v>
+      </x:c>
+      <x:c r="L24"/>
+      <x:c r="M24"/>
+      <x:c r="N24"/>
+      <x:c r="O24" t="str">
+        <x:v>JV structure established</x:v>
+      </x:c>
+      <x:c r="P24" t="str">
+        <x:v>Shareholders agreement signed</x:v>
+      </x:c>
+      <x:c r="Q24" t="str">
+        <x:v>Investment value and timetable undisclosed</x:v>
+      </x:c>
+      <x:c r="R24" t="str">
+        <x:v>SRC260910_017</x:v>
+      </x:c>
+      <x:c r="S24" t="str">
+        <x:v>https://splash247.com/dp-world-formalises-mombasa-industrial-park-joint-venture/</x:v>
+      </x:c>
+      <x:c r="T24" t="str">
+        <x:v>222 ha project; first phase 40 ha; less than 20 km from Port of Mombasa.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>IDEAL_0024</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C25"/>
+      <x:c r="D25" t="str">
+        <x:v>COMP_ADANI_PORTS</x:v>
+      </x:c>
+      <x:c r="E25"/>
+      <x:c r="F25" t="str">
+        <x:v>Paradip Port Authority</x:v>
+      </x:c>
+      <x:c r="G25" t="str">
+        <x:v>PORTG0357</x:v>
+      </x:c>
+      <x:c r="H25" t="str">
+        <x:v>CQ-I and CQ-II dry-bulk berths, Paradip</x:v>
+      </x:c>
+      <x:c r="I25" t="str">
+        <x:v>Dry bulk terminal</x:v>
+      </x:c>
+      <x:c r="J25" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="K25" t="str">
+        <x:v>30-year BOT concession</x:v>
+      </x:c>
+      <x:c r="L25"/>
+      <x:c r="M25" t="str">
+        <x:v>103000000</x:v>
+      </x:c>
+      <x:c r="N25" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="O25" t="str">
+        <x:v>APSEZ to develop and operate</x:v>
+      </x:c>
+      <x:c r="P25" t="str">
+        <x:v>Letter of award / development</x:v>
+      </x:c>
+      <x:c r="Q25" t="str">
+        <x:v>Competitive award</x:v>
+      </x:c>
+      <x:c r="R25" t="str">
+        <x:v>SRC260910_018</x:v>
+      </x:c>
+      <x:c r="S25" t="str">
+        <x:v>https://splash247.com/adani-lands-30-year-paradip-berth-concession/</x:v>
+      </x:c>
+      <x:c r="T25" t="str">
+        <x:v>Adds 18m tonnes/year mechanised dry-bulk capacity.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/data/08_transactions.xlsx
+++ b/data/08_transactions.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rb923a94c29874aa2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Deals" sheetId="2" r:id="Rede6528bafd54b87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions V125" sheetId="3" r:id="Rf3660c77968b4c73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transaction Approvals" sheetId="4" r:id="Rd4e5b14479404906"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transaction Status History" sheetId="5" r:id="Rfd019edbcbe24b72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transaction Asset Links" sheetId="6" r:id="Racc5572bf58f4005"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vessel Transactions" sheetId="7" r:id="Re64ef46f7ada463f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Control History" sheetId="8" r:id="R8ba48a13be504d47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R50926ac059e0463d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Deals" sheetId="2" r:id="Rf27510e6e35646bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions V125" sheetId="3" r:id="Rb3b78d48a1654a42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transaction Approvals" sheetId="4" r:id="R2578df2c9f8c498a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transaction Status History" sheetId="5" r:id="Ra7f2300a14e1481a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transaction Asset Links" sheetId="6" r:id="Rfcb1e5ebf7964002"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vessel Transactions" sheetId="7" r:id="R71802bf911a74317"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Control History" sheetId="8" r:id="R6805b7c64f054d0d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1845,6 +1845,294 @@
         <x:v>Adds 18m tonnes/year mechanised dry-bulk capacity.</x:v>
       </x:c>
     </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>IDEAL_BF_001</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>2025-02-01</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>2026-01-21</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>COMP_TIL</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>COMP_MARSA_MAROC</x:v>
+      </x:c>
+      <x:c r="F26"/>
+      <x:c r="G26" t="str">
+        <x:v>COMP_WMCT</x:v>
+      </x:c>
+      <x:c r="H26" t="str">
+        <x:v>West Med Container Terminal</x:v>
+      </x:c>
+      <x:c r="I26" t="str">
+        <x:v>Container terminal SPV</x:v>
+      </x:c>
+      <x:c r="J26" t="str">
+        <x:v>Morocco</x:v>
+      </x:c>
+      <x:c r="K26" t="str">
+        <x:v>Minority strategic investment / JV completion</x:v>
+      </x:c>
+      <x:c r="L26" t="str">
+        <x:v>50% - 1 share</x:v>
+      </x:c>
+      <x:c r="M26"/>
+      <x:c r="N26"/>
+      <x:c r="O26" t="str">
+        <x:v>Shared operating/ownership structure</x:v>
+      </x:c>
+      <x:c r="P26" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="Q26" t="str">
+        <x:v>Required approvals received</x:v>
+      </x:c>
+      <x:c r="R26" t="str">
+        <x:v>SRC_BF_NADOR_MARSA26</x:v>
+      </x:c>
+      <x:c r="S26" t="str">
+        <x:v>https://www.marsamaroc.co.ma/sites/default/files/2026-01/CP%20%20WEST%20MED%20CONTAINER%20TERMINAL%20UK.pdf</x:v>
+      </x:c>
+      <x:c r="T26" t="str">
+        <x:v>Partnership signed Feb 2025; transaction completed Jan 2026.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>IDEAL_BF_002</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>2022-02-17</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>2022-03-01</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>COMP_CMA_TERMINALS</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>COMP_CMA_CGM</x:v>
+      </x:c>
+      <x:c r="F27" t="str">
+        <x:v>Port of Beirut</x:v>
+      </x:c>
+      <x:c r="G27" t="str">
+        <x:v>TERM_BEIRUT_CT</x:v>
+      </x:c>
+      <x:c r="H27" t="str">
+        <x:v>Port of Beirut Container Terminal</x:v>
+      </x:c>
+      <x:c r="I27" t="str">
+        <x:v>Container terminal</x:v>
+      </x:c>
+      <x:c r="J27" t="str">
+        <x:v>Lebanon</x:v>
+      </x:c>
+      <x:c r="K27" t="str">
+        <x:v>10-year operating concession / modernization commitment</x:v>
+      </x:c>
+      <x:c r="L27"/>
+      <x:c r="M27" t="n">
+        <x:v>33000000</x:v>
+      </x:c>
+      <x:c r="N27" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="O27" t="str">
+        <x:v>CMA Terminals management, operation and maintenance</x:v>
+      </x:c>
+      <x:c r="P27" t="str">
+        <x:v>Operating</x:v>
+      </x:c>
+      <x:c r="Q27" t="str">
+        <x:v>Awarded after bidding process</x:v>
+      </x:c>
+      <x:c r="R27" t="str">
+        <x:v>SRC_BF_BEIRUT_CMA22</x:v>
+      </x:c>
+      <x:c r="S27" t="str">
+        <x:v>https://www.cmacgm-group.com/en/news-media/the-cma-cgm-group-was-awarded-the-concession-of-the-beirut-port-container-terminal-and-foresees-an-ambitious-development-plan</x:v>
+      </x:c>
+      <x:c r="T27" t="str">
+        <x:v>Concession began March 2022; 1.4m TEU target at award.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>IDEAL_BF_003</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C28"/>
+      <x:c r="D28" t="str">
+        <x:v>COMP_NELTUME</x:v>
+      </x:c>
+      <x:c r="E28"/>
+      <x:c r="F28" t="str">
+        <x:v>Government of Uruguay</x:v>
+      </x:c>
+      <x:c r="G28" t="str">
+        <x:v>TERM_MCT_MONTEVIDEO</x:v>
+      </x:c>
+      <x:c r="H28" t="str">
+        <x:v>Montevideo Container Terminal (MCT)</x:v>
+      </x:c>
+      <x:c r="I28" t="str">
+        <x:v>Greenfield container terminal</x:v>
+      </x:c>
+      <x:c r="J28" t="str">
+        <x:v>Uruguay</x:v>
+      </x:c>
+      <x:c r="K28" t="str">
+        <x:v>Privately initiated project proposal</x:v>
+      </x:c>
+      <x:c r="L28"/>
+      <x:c r="M28" t="n">
+        <x:v>900000000</x:v>
+      </x:c>
+      <x:c r="N28" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="O28" t="str">
+        <x:v>Proposed Neltume development</x:v>
+      </x:c>
+      <x:c r="P28" t="str">
+        <x:v>Government evaluation</x:v>
+      </x:c>
+      <x:c r="Q28" t="str">
+        <x:v>No concession structure/timetable disclosed</x:v>
+      </x:c>
+      <x:c r="R28" t="str">
+        <x:v>SRC_BF_NELTUME_SPLASH</x:v>
+      </x:c>
+      <x:c r="S28" t="str">
+        <x:v>https://splash247.com/neltume-pitches-900m-montevideo-container-terminal/</x:v>
+      </x:c>
+      <x:c r="T28" t="str">
+        <x:v>Proposal follows withdrawal of Neltume ICSID arbitration.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>IDEAL_BF_004</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>2018-09-01</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>2018-09-01</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>COMP_ATCO</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>COMP_ULTRAMAR</x:v>
+      </x:c>
+      <x:c r="F29"/>
+      <x:c r="G29" t="str">
+        <x:v>COMP_NELTUME</x:v>
+      </x:c>
+      <x:c r="H29" t="str">
+        <x:v>Neltume Ports</x:v>
+      </x:c>
+      <x:c r="I29" t="str">
+        <x:v>Port operator / infrastructure platform</x:v>
+      </x:c>
+      <x:c r="J29" t="str">
+        <x:v>South America</x:v>
+      </x:c>
+      <x:c r="K29" t="str">
+        <x:v>Minority equity acquisition</x:v>
+      </x:c>
+      <x:c r="L29" t="str">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="M29"/>
+      <x:c r="N29"/>
+      <x:c r="O29" t="str">
+        <x:v>Non-controlled strategic interest</x:v>
+      </x:c>
+      <x:c r="P29" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="Q29" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="R29" t="str">
+        <x:v>SRC_BF_ATCO_NELTUME</x:v>
+      </x:c>
+      <x:c r="S29" t="str">
+        <x:v>https://www.atco.com/en-ca/businesses/investments/neltume-ports.html</x:v>
+      </x:c>
+      <x:c r="T29" t="str">
+        <x:v>ATCO acquired 40% interest in 2018.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>IDEAL_BF_005</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>2021-02-01</x:v>
+      </x:c>
+      <x:c r="C30"/>
+      <x:c r="D30" t="str">
+        <x:v>COMP_KATOEN_NATIE</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>COMP_ANP_URUGUAY</x:v>
+      </x:c>
+      <x:c r="F30" t="str">
+        <x:v>Government of Uruguay</x:v>
+      </x:c>
+      <x:c r="G30" t="str">
+        <x:v>COMP_TCP</x:v>
+      </x:c>
+      <x:c r="H30" t="str">
+        <x:v>Terminal Cuenca del Plata / long-term expansion</x:v>
+      </x:c>
+      <x:c r="I30" t="str">
+        <x:v>Container terminal</x:v>
+      </x:c>
+      <x:c r="J30" t="str">
+        <x:v>Uruguay</x:v>
+      </x:c>
+      <x:c r="K30" t="str">
+        <x:v>Concession extension / expansion commitment</x:v>
+      </x:c>
+      <x:c r="L30" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="M30" t="n">
+        <x:v>600000000</x:v>
+      </x:c>
+      <x:c r="N30" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="O30" t="str">
+        <x:v>Katoen Natie/TCP majority operating control</x:v>
+      </x:c>
+      <x:c r="P30" t="str">
+        <x:v>Active / development</x:v>
+      </x:c>
+      <x:c r="Q30" t="str">
+        <x:v>Environmental works authorization reported in 2023</x:v>
+      </x:c>
+      <x:c r="R30" t="str">
+        <x:v>SRC_BF_TCP_ANP</x:v>
+      </x:c>
+      <x:c r="S30" t="str">
+        <x:v>https://www.anp.com.uy/en/node/1154</x:v>
+      </x:c>
+      <x:c r="T30" t="str">
+        <x:v>ANP says &gt;US$600m expansion; 80% private / 20% ANP structure. Splash cites concession extension to 2081.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2687,6 +2975,121 @@
         <x:v>Company and fleet exposure</x:v>
       </x:c>
     </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>TALINK_BF_001</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>IDEAL_BF_001</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>TERM_NADOR_EAST</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>Nador West Med Eastern Container Terminal</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>TARGET / CONCESSION_ASSET</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G13" t="str">
+        <x:v>WMCT is concessionaire of the terminal.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>TALINK_BF_002</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>IDEAL_BF_002</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>TERM_BEIRUT_CT</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>Port of Beirut Container Terminal</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>CONCESSION_ASSET</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>CMA Terminals operating concession.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>TALINK_BF_003</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>IDEAL_BF_003</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>TERM_MCT_MONTEVIDEO</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>Montevideo Container Terminal (MCT)</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>PROPOSED_ASSET</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G15" t="str">
+        <x:v>US$900m greenfield proposal.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>TALINK_BF_004</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>IDEAL_BF_003</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>PORTG0206</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Port of Montevideo</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>LOCATION / NETWORK</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>Project proposed within Montevideo gateway.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>TALINK_BF_005</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>IDEAL_BF_005</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>TERM_TCP_MONTEVIDEO</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>Terminal Cuenca del Plata</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>CONCESSION_ASSET</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>Long-term container-terminal expansion.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/data/08_transactions.xlsx
+++ b/data/08_transactions.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R50926ac059e0463d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Deals" sheetId="2" r:id="Rf27510e6e35646bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions V125" sheetId="3" r:id="Rb3b78d48a1654a42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transaction Approvals" sheetId="4" r:id="R2578df2c9f8c498a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transaction Status History" sheetId="5" r:id="Ra7f2300a14e1481a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transaction Asset Links" sheetId="6" r:id="Rfcb1e5ebf7964002"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vessel Transactions" sheetId="7" r:id="R71802bf911a74317"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Control History" sheetId="8" r:id="R6805b7c64f054d0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R13c004b74d1c4c10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infra Deals" sheetId="2" r:id="R9ebd31a8130c4250"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions V125" sheetId="3" r:id="R3d1f6b47ca9c4c74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transaction Approvals" sheetId="4" r:id="R27cd6e7593db4838"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transaction Status History" sheetId="5" r:id="R40538f4ed58d4300"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transaction Asset Links" sheetId="6" r:id="R8257455d859e4255"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vessel Transactions" sheetId="7" r:id="R03d816697dd14a1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Control History" sheetId="8" r:id="Rfbc0030ea9674ac1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FX Normalization" sheetId="9" r:id="R29b8440a0c174ebe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,6 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="3">
+    <x:numFmt numFmtId="200" formatCode="#,##0"/>
+    <x:numFmt numFmtId="201" formatCode="0.00000"/>
+    <x:numFmt numFmtId="202" formatCode="$#,##0.00"/>
+  </x:numFmts>
   <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
@@ -44,7 +50,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -61,6 +67,11 @@
         <x:fgColor rgb="FFC5A253"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -69,7 +80,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="23">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -92,6 +103,21 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2133,6 +2159,122 @@
         <x:v>ANP says &gt;US$600m expansion; 80% private / 20% ANP structure. Splash cites concession extension to 2081.</x:v>
       </x:c>
     </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>IDEAL_SAGAR_001</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>2024-07-16</x:v>
+      </x:c>
+      <x:c r="C31"/>
+      <x:c r="D31" t="str">
+        <x:v>GOV_NCPOR</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>COMP_GRSE</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>Government of India / MoES</x:v>
+      </x:c>
+      <x:c r="G31" t="str">
+        <x:v>VESSEL_SAGAR_MANTHAN</x:v>
+      </x:c>
+      <x:c r="H31" t="str">
+        <x:v>ORV Sagar Manthan / Yard 3041</x:v>
+      </x:c>
+      <x:c r="I31" t="str">
+        <x:v>Research vessel / shipbuilding</x:v>
+      </x:c>
+      <x:c r="J31" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="K31" t="str">
+        <x:v>Government procurement / shipbuilding contract</x:v>
+      </x:c>
+      <x:c r="L31"/>
+      <x:c r="M31" t="n">
+        <x:v>100502512.56</x:v>
+      </x:c>
+      <x:c r="N31" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="O31" t="str">
+        <x:v>NCPOR/MoES customer; GRSE builder</x:v>
+      </x:c>
+      <x:c r="P31" t="str">
+        <x:v>Active / launched</x:v>
+      </x:c>
+      <x:c r="Q31" t="str">
+        <x:v>Government contract; delivery now scheduled 2028</x:v>
+      </x:c>
+      <x:c r="R31" t="str">
+        <x:v>SRC_SAGAR_GRSE_CONTRACT</x:v>
+      </x:c>
+      <x:c r="S31" t="str">
+        <x:v>https://www.grse.in/corporate-announcement/files/Signing_of_Contract_for_construction_and_delivery_of_ORV_for_NCPOR.pdf</x:v>
+      </x:c>
+      <x:c r="T31" t="str">
+        <x:v>Primary contract value ₹840 crore (INR 8,400,000,000); USD normalized at historical 16 Jul 2024 rate ₹83.58/USD = ~US$100.50m.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>IDEAL_SAGAR_002</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>2024-10-29</x:v>
+      </x:c>
+      <x:c r="C32"/>
+      <x:c r="D32" t="str">
+        <x:v>GOV_NPOL</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>COMP_GRSE</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>DRDO / Government of India</x:v>
+      </x:c>
+      <x:c r="G32" t="str">
+        <x:v>VESSEL_ARS_3058</x:v>
+      </x:c>
+      <x:c r="H32" t="str">
+        <x:v>Acoustic Research Ship / Yard 3058</x:v>
+      </x:c>
+      <x:c r="I32" t="str">
+        <x:v>Research vessel / defence R&amp;D shipbuilding</x:v>
+      </x:c>
+      <x:c r="J32" t="str">
+        <x:v>India</x:v>
+      </x:c>
+      <x:c r="K32" t="str">
+        <x:v>Government procurement / shipbuilding contract</x:v>
+      </x:c>
+      <x:c r="L32"/>
+      <x:c r="M32" t="n">
+        <x:v>58404152.74</x:v>
+      </x:c>
+      <x:c r="N32" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="O32" t="str">
+        <x:v>NPOL/DRDO customer; GRSE builder</x:v>
+      </x:c>
+      <x:c r="P32" t="str">
+        <x:v>Active / under construction</x:v>
+      </x:c>
+      <x:c r="Q32" t="str">
+        <x:v>Domestic government R&amp;D contract</x:v>
+      </x:c>
+      <x:c r="R32" t="str">
+        <x:v>SRC_SAGAR_GRSE_ARS</x:v>
+      </x:c>
+      <x:c r="S32" t="str">
+        <x:v>https://www.grse.in/corporate-announcement/files/Reg_30_GRSE_signed_Contract_for_One_Acoustic_Research_Ship_%28ARS%29_for_NPOL_Kochi_and_Press_Release.pdf</x:v>
+      </x:c>
+      <x:c r="T32" t="str">
+        <x:v>Primary contract value ₹490.98 crore (INR 4,909,800,000); USD normalized at historical 29 Oct 2024 rate ₹84.06594/USD = ~US$58.40m.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3270,4 +3412,103 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="46" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="19" t="str">
+        <x:v>Record ID</x:v>
+      </x:c>
+      <x:c r="B1" s="19" t="str">
+        <x:v>Programme / Contract</x:v>
+      </x:c>
+      <x:c r="C1" s="19" t="str">
+        <x:v>Native Value (INR)</x:v>
+      </x:c>
+      <x:c r="D1" s="19" t="str">
+        <x:v>Contract Date</x:v>
+      </x:c>
+      <x:c r="E1" s="19" t="str">
+        <x:v>INR per USD</x:v>
+      </x:c>
+      <x:c r="F1" s="19" t="str">
+        <x:v>USD Equivalent</x:v>
+      </x:c>
+      <x:c r="G1" s="19" t="str">
+        <x:v>FX Source URL</x:v>
+      </x:c>
+      <x:c r="H1" s="19" t="str">
+        <x:v>Method</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="14" t="str">
+        <x:v>IDEAL_SAGAR_001</x:v>
+      </x:c>
+      <x:c r="B2" s="14" t="str">
+        <x:v>ORV Sagar Manthan / Yard 3041</x:v>
+      </x:c>
+      <x:c r="C2" s="20" t="n">
+        <x:v>8400000000</x:v>
+      </x:c>
+      <x:c r="D2" s="14" t="str">
+        <x:v>2024-07-16</x:v>
+      </x:c>
+      <x:c r="E2" s="21" t="n">
+        <x:v>83.58</x:v>
+      </x:c>
+      <x:c r="F2" s="22" t="n">
+        <x:f>C2/E2</x:f>
+        <x:v>100502512.56281407</x:v>
+      </x:c>
+      <x:c r="G2" s="14" t="str">
+        <x:v>https://www.exchange-rates.org/exchange-rate-history/usd-inr-2024-07-16</x:v>
+      </x:c>
+      <x:c r="H2" s="14" t="str">
+        <x:v>Historical contract-date conversion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="14" t="str">
+        <x:v>IDEAL_SAGAR_002</x:v>
+      </x:c>
+      <x:c r="B3" s="14" t="str">
+        <x:v>Acoustic Research Ship / Yard 3058</x:v>
+      </x:c>
+      <x:c r="C3" s="20" t="n">
+        <x:v>4909800000</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="str">
+        <x:v>2024-10-29</x:v>
+      </x:c>
+      <x:c r="E3" s="21" t="n">
+        <x:v>84.06594</x:v>
+      </x:c>
+      <x:c r="F3" s="22" t="n">
+        <x:f>C3/E3</x:f>
+        <x:v>58404152.74009902</x:v>
+      </x:c>
+      <x:c r="G3" s="14" t="str">
+        <x:v>https://www.exchange-rates.org/exchange-rate-history/usd-inr-2024-10-29</x:v>
+      </x:c>
+      <x:c r="H3" s="14" t="str">
+        <x:v>Historical contract-date conversion</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>